--- a/artfynd/A 28183-2026 artfynd.xlsx
+++ b/artfynd/A 28183-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665018</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665251</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665260</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665032</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665033</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665250</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1444,6 +1479,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665252</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1550,6 +1590,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665253</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1656,6 +1701,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665254</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665255</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1868,6 +1923,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665256</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1974,6 +2034,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665257</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2080,6 +2145,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665258</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2186,6 +2256,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665262</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2292,6 +2367,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665263</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2398,8 +2478,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665261</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28183-2026 artfynd.xlsx
+++ b/artfynd/A 28183-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134665018</v>
+        <v>135888150</v>
       </c>
       <c r="B2" t="n">
-        <v>80488</v>
+        <v>93337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>801286</v>
+        <v>801175</v>
       </c>
       <c r="R2" t="n">
-        <v>7353713</v>
+        <v>7353809</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,16 +795,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665018</t>
+          <t>https://artportalen.se/Sighting/135888150</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134665251</v>
+        <v>135888166</v>
       </c>
       <c r="B3" t="n">
-        <v>80488</v>
+        <v>93339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,26 +812,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801286</v>
+        <v>801149</v>
       </c>
       <c r="R3" t="n">
-        <v>7353710</v>
+        <v>7353811</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,12 +870,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -906,38 +916,38 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665251</t>
+          <t>https://artportalen.se/Sighting/135888166</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134665260</v>
+        <v>134665018</v>
       </c>
       <c r="B4" t="n">
-        <v>99112</v>
+        <v>80488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>801111</v>
+        <v>801286</v>
       </c>
       <c r="R4" t="n">
-        <v>7353822</v>
+        <v>7353713</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,12 +991,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1017,43 +1037,43 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665260</t>
+          <t>https://artportalen.se/Sighting/134665018</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134665032</v>
+        <v>134665251</v>
       </c>
       <c r="B5" t="n">
-        <v>99195</v>
+        <v>80488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1062,13 +1082,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>801234</v>
+        <v>801286</v>
       </c>
       <c r="R5" t="n">
-        <v>7353729</v>
+        <v>7353710</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,19 +1115,9 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>08:57</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>08:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1138,43 +1148,43 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665032</t>
+          <t>https://artportalen.se/Sighting/134665251</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134665033</v>
+        <v>134665260</v>
       </c>
       <c r="B6" t="n">
-        <v>99195</v>
+        <v>99112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1183,13 +1193,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801243</v>
+        <v>801111</v>
       </c>
       <c r="R6" t="n">
-        <v>7353727</v>
+        <v>7353822</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,22 +1223,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>08:56</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>08:56</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1259,13 +1259,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665033</t>
+          <t>https://artportalen.se/Sighting/134665260</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134665250</v>
+        <v>134665032</v>
       </c>
       <c r="B7" t="n">
         <v>99195</v>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801098</v>
+        <v>801234</v>
       </c>
       <c r="R7" t="n">
-        <v>7353832</v>
+        <v>7353729</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,9 +1337,19 @@
           <t>2026-06-17</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1370,13 +1380,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665250</t>
+          <t>https://artportalen.se/Sighting/134665032</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134665252</v>
+        <v>134665033</v>
       </c>
       <c r="B8" t="n">
         <v>99195</v>
@@ -1406,7 +1416,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1415,13 +1425,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>801259</v>
+        <v>801243</v>
       </c>
       <c r="R8" t="n">
-        <v>7353745</v>
+        <v>7353727</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1448,9 +1458,19 @@
           <t>2026-06-17</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1481,13 +1501,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665252</t>
+          <t>https://artportalen.se/Sighting/134665033</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134665253</v>
+        <v>134665250</v>
       </c>
       <c r="B9" t="n">
         <v>99195</v>
@@ -1517,7 +1537,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1526,10 +1546,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801268</v>
+        <v>801098</v>
       </c>
       <c r="R9" t="n">
-        <v>7353750</v>
+        <v>7353832</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,13 +1612,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665253</t>
+          <t>https://artportalen.se/Sighting/134665250</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134665254</v>
+        <v>134665252</v>
       </c>
       <c r="B10" t="n">
         <v>99195</v>
@@ -1628,7 +1648,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1637,10 +1657,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>801284</v>
+        <v>801259</v>
       </c>
       <c r="R10" t="n">
-        <v>7353735</v>
+        <v>7353745</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1703,13 +1723,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665254</t>
+          <t>https://artportalen.se/Sighting/134665252</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134665255</v>
+        <v>134665253</v>
       </c>
       <c r="B11" t="n">
         <v>99195</v>
@@ -1739,7 +1759,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1748,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801296</v>
+        <v>801268</v>
       </c>
       <c r="R11" t="n">
-        <v>7353752</v>
+        <v>7353750</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1814,13 +1834,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665255</t>
+          <t>https://artportalen.se/Sighting/134665253</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134665256</v>
+        <v>134665254</v>
       </c>
       <c r="B12" t="n">
         <v>99195</v>
@@ -1850,7 +1870,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>130</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1859,10 +1879,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801303</v>
+        <v>801284</v>
       </c>
       <c r="R12" t="n">
-        <v>7353774</v>
+        <v>7353735</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1925,13 +1945,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665256</t>
+          <t>https://artportalen.se/Sighting/134665254</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134665257</v>
+        <v>134665255</v>
       </c>
       <c r="B13" t="n">
         <v>99195</v>
@@ -1961,7 +1981,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1970,10 +1990,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801299</v>
+        <v>801296</v>
       </c>
       <c r="R13" t="n">
-        <v>7353758</v>
+        <v>7353752</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2036,13 +2056,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665257</t>
+          <t>https://artportalen.se/Sighting/134665255</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134665258</v>
+        <v>134665256</v>
       </c>
       <c r="B14" t="n">
         <v>99195</v>
@@ -2072,7 +2092,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2081,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801287</v>
+        <v>801303</v>
       </c>
       <c r="R14" t="n">
-        <v>7353768</v>
+        <v>7353774</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2147,13 +2167,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665258</t>
+          <t>https://artportalen.se/Sighting/134665256</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134665262</v>
+        <v>134665257</v>
       </c>
       <c r="B15" t="n">
         <v>99195</v>
@@ -2183,7 +2203,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2192,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>801114</v>
+        <v>801299</v>
       </c>
       <c r="R15" t="n">
-        <v>7353817</v>
+        <v>7353758</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,12 +2242,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2258,13 +2278,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665262</t>
+          <t>https://artportalen.se/Sighting/134665257</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134665263</v>
+        <v>134665258</v>
       </c>
       <c r="B16" t="n">
         <v>99195</v>
@@ -2294,7 +2314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2303,10 +2323,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801275</v>
+        <v>801287</v>
       </c>
       <c r="R16" t="n">
-        <v>7353726</v>
+        <v>7353768</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2333,12 +2353,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2369,43 +2389,43 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665263</t>
+          <t>https://artportalen.se/Sighting/134665258</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134665261</v>
+        <v>134665262</v>
       </c>
       <c r="B17" t="n">
-        <v>106324</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2414,7 +2434,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801113</v>
+        <v>801114</v>
       </c>
       <c r="R17" t="n">
         <v>7353817</v>
@@ -2479,6 +2499,228 @@
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665262</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134665263</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>801275</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7353726</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665263</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134665261</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>801113</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7353817</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134665261</t>
         </is>
@@ -2502,6 +2744,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28183-2026 artfynd.xlsx
+++ b/artfynd/A 28183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888150</v>
       </c>
       <c r="B2" t="n">
-        <v>93337</v>
+        <v>93339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135888166</v>
       </c>
       <c r="B3" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28183-2026 artfynd.xlsx
+++ b/artfynd/A 28183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888150</v>
       </c>
       <c r="B2" t="n">
-        <v>93339</v>
+        <v>93354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135888166</v>
       </c>
       <c r="B3" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28183-2026 artfynd.xlsx
+++ b/artfynd/A 28183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888150</v>
       </c>
       <c r="B2" t="n">
-        <v>93354</v>
+        <v>93355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135888166</v>
       </c>
       <c r="B3" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28183-2026 artfynd.xlsx
+++ b/artfynd/A 28183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888150</v>
       </c>
       <c r="B2" t="n">
-        <v>93355</v>
+        <v>93356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135888166</v>
       </c>
       <c r="B3" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28183-2026 artfynd.xlsx
+++ b/artfynd/A 28183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888150</v>
       </c>
       <c r="B2" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135888166</v>
       </c>
       <c r="B3" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28183-2026 artfynd.xlsx
+++ b/artfynd/A 28183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888150</v>
       </c>
       <c r="B2" t="n">
-        <v>93357</v>
+        <v>93363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135888166</v>
       </c>
       <c r="B3" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28183-2026 artfynd.xlsx
+++ b/artfynd/A 28183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888150</v>
       </c>
       <c r="B2" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135888166</v>
       </c>
       <c r="B3" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28183-2026 artfynd.xlsx
+++ b/artfynd/A 28183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888150</v>
       </c>
       <c r="B2" t="n">
-        <v>93364</v>
+        <v>93370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135888166</v>
       </c>
       <c r="B3" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28183-2026 artfynd.xlsx
+++ b/artfynd/A 28183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888150</v>
       </c>
       <c r="B2" t="n">
-        <v>93370</v>
+        <v>93377</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135888166</v>
       </c>
       <c r="B3" t="n">
-        <v>93372</v>
+        <v>93379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28183-2026 artfynd.xlsx
+++ b/artfynd/A 28183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888150</v>
       </c>
       <c r="B2" t="n">
-        <v>93377</v>
+        <v>93378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135888166</v>
       </c>
       <c r="B3" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28183-2026 artfynd.xlsx
+++ b/artfynd/A 28183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888150</v>
       </c>
       <c r="B2" t="n">
-        <v>93378</v>
+        <v>93391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135888166</v>
       </c>
       <c r="B3" t="n">
-        <v>93380</v>
+        <v>93393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28183-2026 artfynd.xlsx
+++ b/artfynd/A 28183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888150</v>
       </c>
       <c r="B2" t="n">
-        <v>93391</v>
+        <v>93392</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135888166</v>
       </c>
       <c r="B3" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
